--- a/artfynd/A 6903-2024 artfynd.xlsx
+++ b/artfynd/A 6903-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121154721</v>
       </c>
       <c r="B2" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 6903-2024 artfynd.xlsx
+++ b/artfynd/A 6903-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121154721</v>
       </c>
       <c r="B2" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 6903-2024 artfynd.xlsx
+++ b/artfynd/A 6903-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121154721</v>
       </c>
       <c r="B2" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 6903-2024 artfynd.xlsx
+++ b/artfynd/A 6903-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>121154721</v>
       </c>
       <c r="B2" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,6 +784,108 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>121515232</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79688</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Norrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>563509</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6992912</v>
+      </c>
+      <c r="S3" t="n">
+        <v>100</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6903-2024 artfynd.xlsx
+++ b/artfynd/A 6903-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>121515232</v>
       </c>
       <c r="B3" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 6903-2024 artfynd.xlsx
+++ b/artfynd/A 6903-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>121515232</v>
       </c>
       <c r="B3" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 6903-2024 artfynd.xlsx
+++ b/artfynd/A 6903-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>121515232</v>
       </c>
       <c r="B3" t="n">
-        <v>79690</v>
+        <v>79697</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 6903-2024 artfynd.xlsx
+++ b/artfynd/A 6903-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -887,6 +887,516 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125171799</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Norrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>563584</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6992951</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125171880</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bengtdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>563546</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6993040</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125171960</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Norrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>563531</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6993029</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125171869</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Norrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>563557</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6992990</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125171691</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bengtdalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>563578</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6993076</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6903-2024 artfynd.xlsx
+++ b/artfynd/A 6903-2024 artfynd.xlsx
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125171880</v>
+        <v>125171691</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563546</v>
+        <v>563578</v>
       </c>
       <c r="R5" t="n">
-        <v>6993040</v>
+        <v>6993076</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1195,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125171869</v>
+        <v>125171880</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1231,14 +1231,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Norrberget, Jmt</t>
+          <t>Bengtdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563557</v>
+        <v>563546</v>
       </c>
       <c r="R7" t="n">
-        <v>6992990</v>
+        <v>6993040</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125171691</v>
+        <v>125171869</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1333,14 +1333,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bengtdalsbäcken, Jmt</t>
+          <t>Norrberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563578</v>
+        <v>563557</v>
       </c>
       <c r="R8" t="n">
-        <v>6993076</v>
+        <v>6992990</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>

--- a/artfynd/A 6903-2024 artfynd.xlsx
+++ b/artfynd/A 6903-2024 artfynd.xlsx
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125171691</v>
+        <v>125171960</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1027,14 +1027,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bengtdalsbäcken, Jmt</t>
+          <t>Norrberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563578</v>
+        <v>563531</v>
       </c>
       <c r="R5" t="n">
-        <v>6993076</v>
+        <v>6993029</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1093,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125171960</v>
+        <v>125171880</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1129,14 +1129,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norrberget, Jmt</t>
+          <t>Bengtdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563531</v>
+        <v>563546</v>
       </c>
       <c r="R6" t="n">
-        <v>6993029</v>
+        <v>6993040</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1195,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125171880</v>
+        <v>125171869</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1231,14 +1231,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bengtdalsbäcken, Jmt</t>
+          <t>Norrberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563546</v>
+        <v>563557</v>
       </c>
       <c r="R7" t="n">
-        <v>6993040</v>
+        <v>6992990</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125171869</v>
+        <v>125171691</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1333,14 +1333,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Norrberget, Jmt</t>
+          <t>Bengtdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563557</v>
+        <v>563578</v>
       </c>
       <c r="R8" t="n">
-        <v>6992990</v>
+        <v>6993076</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>

--- a/artfynd/A 6903-2024 artfynd.xlsx
+++ b/artfynd/A 6903-2024 artfynd.xlsx
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125171799</v>
+        <v>125171880</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -925,14 +925,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norrberget, Jmt</t>
+          <t>Bengtdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563584</v>
+        <v>563546</v>
       </c>
       <c r="R4" t="n">
-        <v>6992951</v>
+        <v>6993040</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125171960</v>
+        <v>125171799</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563531</v>
+        <v>563584</v>
       </c>
       <c r="R5" t="n">
-        <v>6993029</v>
+        <v>6992951</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1093,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125171880</v>
+        <v>125171691</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563546</v>
+        <v>563578</v>
       </c>
       <c r="R6" t="n">
-        <v>6993040</v>
+        <v>6993076</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125171691</v>
+        <v>125171960</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1333,14 +1333,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bengtdalsbäcken, Jmt</t>
+          <t>Norrberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563578</v>
+        <v>563531</v>
       </c>
       <c r="R8" t="n">
-        <v>6993076</v>
+        <v>6993029</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>

--- a/artfynd/A 6903-2024 artfynd.xlsx
+++ b/artfynd/A 6903-2024 artfynd.xlsx
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125171880</v>
+        <v>125171799</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -925,14 +925,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bengtdalsbäcken, Jmt</t>
+          <t>Norrberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563546</v>
+        <v>563584</v>
       </c>
       <c r="R4" t="n">
-        <v>6993040</v>
+        <v>6992951</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125171799</v>
+        <v>125171691</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1027,14 +1027,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norrberget, Jmt</t>
+          <t>Bengtdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563584</v>
+        <v>563578</v>
       </c>
       <c r="R5" t="n">
-        <v>6992951</v>
+        <v>6993076</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1093,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125171691</v>
+        <v>125171960</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1129,14 +1129,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bengtdalsbäcken, Jmt</t>
+          <t>Norrberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563578</v>
+        <v>563531</v>
       </c>
       <c r="R6" t="n">
-        <v>6993076</v>
+        <v>6993029</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1195,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125171869</v>
+        <v>125171880</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1231,14 +1231,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Norrberget, Jmt</t>
+          <t>Bengtdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563557</v>
+        <v>563546</v>
       </c>
       <c r="R7" t="n">
-        <v>6992990</v>
+        <v>6993040</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125171960</v>
+        <v>125171869</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563531</v>
+        <v>563557</v>
       </c>
       <c r="R8" t="n">
-        <v>6993029</v>
+        <v>6992990</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>

--- a/artfynd/A 6903-2024 artfynd.xlsx
+++ b/artfynd/A 6903-2024 artfynd.xlsx
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125171799</v>
+        <v>125171880</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -925,14 +925,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norrberget, Jmt</t>
+          <t>Bengtdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563584</v>
+        <v>563546</v>
       </c>
       <c r="R4" t="n">
-        <v>6992951</v>
+        <v>6993040</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1093,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125171960</v>
+        <v>125171869</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563531</v>
+        <v>563557</v>
       </c>
       <c r="R6" t="n">
-        <v>6993029</v>
+        <v>6992990</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1195,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125171880</v>
+        <v>125171960</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1231,14 +1231,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bengtdalsbäcken, Jmt</t>
+          <t>Norrberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563546</v>
+        <v>563531</v>
       </c>
       <c r="R7" t="n">
-        <v>6993040</v>
+        <v>6993029</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125171869</v>
+        <v>125171799</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563557</v>
+        <v>563584</v>
       </c>
       <c r="R8" t="n">
-        <v>6992990</v>
+        <v>6992951</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>

--- a/artfynd/A 6903-2024 artfynd.xlsx
+++ b/artfynd/A 6903-2024 artfynd.xlsx
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125171880</v>
+        <v>125171869</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -925,14 +925,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bengtdalsbäcken, Jmt</t>
+          <t>Norrberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563546</v>
+        <v>563557</v>
       </c>
       <c r="R4" t="n">
-        <v>6993040</v>
+        <v>6992990</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125171691</v>
+        <v>125171960</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1027,14 +1027,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bengtdalsbäcken, Jmt</t>
+          <t>Norrberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563578</v>
+        <v>563531</v>
       </c>
       <c r="R5" t="n">
-        <v>6993076</v>
+        <v>6993029</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1093,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125171869</v>
+        <v>125171691</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1129,14 +1129,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norrberget, Jmt</t>
+          <t>Bengtdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563557</v>
+        <v>563578</v>
       </c>
       <c r="R6" t="n">
-        <v>6992990</v>
+        <v>6993076</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1195,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125171960</v>
+        <v>125171880</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1231,14 +1231,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Norrberget, Jmt</t>
+          <t>Bengtdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563531</v>
+        <v>563546</v>
       </c>
       <c r="R7" t="n">
-        <v>6993029</v>
+        <v>6993040</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>

--- a/artfynd/A 6903-2024 artfynd.xlsx
+++ b/artfynd/A 6903-2024 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125171869</v>
+        <v>125171691</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,14 +925,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norrberget, Jmt</t>
+          <t>Bengtdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563557</v>
+        <v>563578</v>
       </c>
       <c r="R4" t="n">
-        <v>6992990</v>
+        <v>6993076</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125171960</v>
+        <v>125171799</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563531</v>
+        <v>563584</v>
       </c>
       <c r="R5" t="n">
-        <v>6993029</v>
+        <v>6992951</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125171691</v>
+        <v>125171869</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,14 +1129,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bengtdalsbäcken, Jmt</t>
+          <t>Norrberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563578</v>
+        <v>563557</v>
       </c>
       <c r="R6" t="n">
-        <v>6993076</v>
+        <v>6992990</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1198,7 +1198,7 @@
         <v>125171880</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125171799</v>
+        <v>125171960</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563584</v>
+        <v>563531</v>
       </c>
       <c r="R8" t="n">
-        <v>6992951</v>
+        <v>6993029</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>

--- a/artfynd/A 6903-2024 artfynd.xlsx
+++ b/artfynd/A 6903-2024 artfynd.xlsx
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125171691</v>
+        <v>125171799</v>
       </c>
       <c r="B4" t="n">
         <v>98269</v>
@@ -925,14 +925,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bengtdalsbäcken, Jmt</t>
+          <t>Norrberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563578</v>
+        <v>563584</v>
       </c>
       <c r="R4" t="n">
-        <v>6993076</v>
+        <v>6992951</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125171799</v>
+        <v>125171960</v>
       </c>
       <c r="B5" t="n">
         <v>98269</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563584</v>
+        <v>563531</v>
       </c>
       <c r="R5" t="n">
-        <v>6992951</v>
+        <v>6993029</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1093,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125171869</v>
+        <v>125171880</v>
       </c>
       <c r="B6" t="n">
         <v>98269</v>
@@ -1129,14 +1129,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norrberget, Jmt</t>
+          <t>Bengtdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563557</v>
+        <v>563546</v>
       </c>
       <c r="R6" t="n">
-        <v>6992990</v>
+        <v>6993040</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1195,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125171880</v>
+        <v>125171869</v>
       </c>
       <c r="B7" t="n">
         <v>98269</v>
@@ -1231,14 +1231,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bengtdalsbäcken, Jmt</t>
+          <t>Norrberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563546</v>
+        <v>563557</v>
       </c>
       <c r="R7" t="n">
-        <v>6993040</v>
+        <v>6992990</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125171960</v>
+        <v>125171691</v>
       </c>
       <c r="B8" t="n">
         <v>98269</v>
@@ -1333,14 +1333,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Norrberget, Jmt</t>
+          <t>Bengtdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563531</v>
+        <v>563578</v>
       </c>
       <c r="R8" t="n">
-        <v>6993029</v>
+        <v>6993076</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>

--- a/artfynd/A 6903-2024 artfynd.xlsx
+++ b/artfynd/A 6903-2024 artfynd.xlsx
@@ -889,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125171799</v>
+        <v>125171869</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563584</v>
+        <v>563557</v>
       </c>
       <c r="R4" t="n">
-        <v>6992951</v>
+        <v>6992990</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -991,15 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125171960</v>
+        <v>125171691</v>
       </c>
       <c r="B5" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,14 +1017,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norrberget, Jmt</t>
+          <t>Bengtdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563531</v>
+        <v>563578</v>
       </c>
       <c r="R5" t="n">
-        <v>6993029</v>
+        <v>6993076</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1093,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125171880</v>
+        <v>125171799</v>
       </c>
       <c r="B6" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,14 +1114,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bengtdalsbäcken, Jmt</t>
+          <t>Norrberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563546</v>
+        <v>563584</v>
       </c>
       <c r="R6" t="n">
-        <v>6993040</v>
+        <v>6992951</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1195,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125171869</v>
+        <v>125171880</v>
       </c>
       <c r="B7" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,14 +1211,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Norrberget, Jmt</t>
+          <t>Bengtdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563557</v>
+        <v>563546</v>
       </c>
       <c r="R7" t="n">
-        <v>6992990</v>
+        <v>6993040</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1297,15 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125171691</v>
+        <v>125171960</v>
       </c>
       <c r="B8" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,14 +1308,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bengtdalsbäcken, Jmt</t>
+          <t>Norrberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563578</v>
+        <v>563531</v>
       </c>
       <c r="R8" t="n">
-        <v>6993076</v>
+        <v>6993029</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>

--- a/artfynd/A 6903-2024 artfynd.xlsx
+++ b/artfynd/A 6903-2024 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>125171869</v>
       </c>
       <c r="B4" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>125171691</v>
       </c>
       <c r="B5" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>125171799</v>
       </c>
       <c r="B6" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>125171880</v>
       </c>
       <c r="B7" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>125171960</v>
       </c>
       <c r="B8" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 6903-2024 artfynd.xlsx
+++ b/artfynd/A 6903-2024 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121154721</v>
+        <v>121515232</v>
       </c>
       <c r="B2" t="n">
-        <v>98098</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:52</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:52</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121515232</v>
+        <v>121154721</v>
       </c>
       <c r="B3" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -857,12 +837,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125171869</v>
+        <v>125171691</v>
       </c>
       <c r="B4" t="n">
-        <v>98331</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,14 +910,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norrberget, Jmt</t>
+          <t>Bengtdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563557</v>
+        <v>563578</v>
       </c>
       <c r="R4" t="n">
-        <v>6992990</v>
+        <v>6993076</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -986,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125171691</v>
+        <v>125171799</v>
       </c>
       <c r="B5" t="n">
-        <v>98331</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,14 +1007,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bengtdalsbäcken, Jmt</t>
+          <t>Norrberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563578</v>
+        <v>563584</v>
       </c>
       <c r="R5" t="n">
-        <v>6993076</v>
+        <v>6992951</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1083,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125171799</v>
+        <v>125171869</v>
       </c>
       <c r="B6" t="n">
-        <v>98331</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563584</v>
+        <v>563557</v>
       </c>
       <c r="R6" t="n">
-        <v>6992951</v>
+        <v>6992990</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1183,7 +1173,7 @@
         <v>125171880</v>
       </c>
       <c r="B7" t="n">
-        <v>98331</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1270,7 @@
         <v>125171960</v>
       </c>
       <c r="B8" t="n">
-        <v>98331</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 6903-2024 artfynd.xlsx
+++ b/artfynd/A 6903-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121515232</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121154721</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125171799</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125171869</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125171880</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125171960</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,8 +1396,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125171691</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>